--- a/data/api_temperature_profiles.xlsx
+++ b/data/api_temperature_profiles.xlsx
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-28 16:36:07Z</t>
+          <t>2026-08-06 11:55:08Z</t>
         </is>
       </c>
     </row>
